--- a/site/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/headings.xlsx
+++ b/site/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,6 +526,116 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01KWVJE3K6FH1P91BN1G558DAM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KWVJE3K6FH1P91BN1G558DAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01KWVJX5C474X9N8HP81NSNEJW</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KWVJX5C474X9N8HP81NSNEJW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01KWVJYFB6K2Z5AFDMXH740HDJ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KWVJYFB6K2Z5AFDMXH740HDJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KWVKXFTPTVSNTJTQ8X76M9F0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KWVKXFTPTVSNTJTQ8X76M9F0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Access Policy</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KWVKYGPN5BSB5A4B7EMKH3BW</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KWVKYGPN5BSB5A4B7EMKH3BW</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/headings.xlsx
+++ b/site/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,6 +636,94 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Role Policy</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KTBJ8WNSMWWRZ3BDTNZWYA3S</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KTBJ8WNSMWWRZ3BDTNZWYA3S</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Required Roles</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KWXFCB5XXB0EQ7PDX130YZBB</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KWXFCB5XXB0EQ7PDX130YZBB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Forbidden Roles</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KWXG3P00165D0YHNP95NQFM9</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KWXG3P00165D0YHNP95NQFM9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Access Profile Policy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KWXG66XRQ0FPBWAE4Y5JPS0Z</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KWXG66XRQ0FPBWAE4Y5JPS0Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/headings.xlsx
+++ b/site/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,6 +724,204 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Required Access Profiles</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KWY7QP7YFJ5E36NDJFN2ZJPD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KWY7QP7YFJ5E36NDJFN2ZJPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Forbidden Access Profiles</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KWY7CM8QJTVY1E7MEMM5SK1W</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KWY7CM8QJTVY1E7MEMM5SK1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Directory Access Policy</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KTC1YYZB438W48Y7PE48WTY0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KTC1YYZB438W48Y7PE48WTY0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Attribute Policy</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KTBHZ41GYMA7WJW3HWQN1P7S</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KTBHZ41GYMA7WJW3HWQN1P7S</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ITSM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KVDADHZ3V8N94HWS36SPY4E3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KVDADHZ3V8N94HWS36SPY4E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Application Configurations</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KVD347BK0V88V2YM4DNMSRV3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KVD347BK0V88V2YM4DNMSRV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Watchdog Insights</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KQ9AKSTAGRHHECR0BZP7CA26</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KQ9AKSTAGRHHECR0BZP7CA26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ITSM Dashboards Created by Watchdog</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KWKCJSCJ2G3JW6BD2DB3S7PN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-BambooHR-SailPoint-ServiceNow-Integration/#h_01KWKCJSCJ2G3JW6BD2DB3S7PN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
